--- a/research/data_sources/DATA_SOURCE_REGISTER.xlsx
+++ b/research/data_sources/DATA_SOURCE_REGISTER.xlsx
@@ -121,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -152,6 +152,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -517,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1888,6 +1891,370 @@
       <c r="J27" s="3" t="inlineStr">
         <is>
           <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>OpenFEMA National Risk Index (direct API)</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>Risk (fire/flood/quake +hazards)</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>Nationwide county/tract</t>
+        </is>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>Periodic</t>
+        </is>
+      </c>
+      <c r="E28" s="12" t="inlineStr">
+        <is>
+          <t>FREE (no key)</t>
+        </is>
+      </c>
+      <c r="F28" s="12" t="inlineStr">
+        <is>
+          <t>Public US Gov data, no registration. Clean terms.</t>
+        </is>
+      </c>
+      <c r="G28" s="12" t="inlineStr">
+        <is>
+          <t>Yes - REST + docs</t>
+        </is>
+      </c>
+      <c r="H28" s="12" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I28" s="12" t="inlineStr">
+        <is>
+          <t>RECOMMEND - hardens insurance-risk moat, usable now</t>
+        </is>
+      </c>
+      <c r="J28" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>USFS Wildfire Risk to Communities</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>Wildfire hazard/burn prob/risk-to-homes</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>Nationwide 30m + community</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>Periodic</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="F29" s="12" t="inlineStr">
+        <is>
+          <t>USFS public; license NOT stated on download page (unverified). GIS/image only, no JSON.</t>
+        </is>
+      </c>
+      <c r="G29" s="12" t="inlineStr">
+        <is>
+          <t>Partial - GIS/image, no JSON</t>
+        </is>
+      </c>
+      <c r="H29" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I29" s="12" t="inlineStr">
+        <is>
+          <t>MAYBE - strongest free wildfire layer but no clean API + verify license</t>
+        </is>
+      </c>
+      <c r="J29" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>Census Building Permits Survey (BPS)</t>
+        </is>
+      </c>
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>New-supply / permits signal</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>Nationwide nat/state/local</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="E30" s="12" t="inlineStr">
+        <is>
+          <t>FREE (free key)</t>
+        </is>
+      </c>
+      <c r="F30" s="12" t="inlineStr">
+        <is>
+          <t>Commercial use OK; must show 'not endorsed by Census' notice; no endorsement implied.</t>
+        </is>
+      </c>
+      <c r="G30" s="12" t="inlineStr">
+        <is>
+          <t>Yes - REST</t>
+        </is>
+      </c>
+      <c r="H30" s="12" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I30" s="12" t="inlineStr">
+        <is>
+          <t>RECOMMEND - free price-context, usable now</t>
+        </is>
+      </c>
+      <c r="J30" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>Census ACS</t>
+        </is>
+      </c>
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>Income/housing/demographics (display-only)</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>Nationwide</t>
+        </is>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>Yearly</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="inlineStr">
+        <is>
+          <t>FREE (free key)</t>
+        </is>
+      </c>
+      <c r="F31" s="12" t="inlineStr">
+        <is>
+          <t>Same Census terms. FAIR-HOUSING: demographics INFO-ONLY, never score/filter.</t>
+        </is>
+      </c>
+      <c r="G31" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H31" s="12" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I31" s="12" t="inlineStr">
+        <is>
+          <t>MAYBE - income context for affordability OK; demographics display-only</t>
+        </is>
+      </c>
+      <c r="J31" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>FRED (St. Louis Fed)</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="inlineStr">
+        <is>
+          <t>Mortgage rate / econ series</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t>Nationwide</t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>Daily/weekly</t>
+        </is>
+      </c>
+      <c r="E32" s="12" t="inlineStr">
+        <is>
+          <t>FREE (free key)</t>
+        </is>
+      </c>
+      <c r="F32" s="12" t="inlineStr">
+        <is>
+          <t>NEW: terms prohibit using content to develop/train software/ML incl. LLMs. We already get rate free from Freddie Mac.</t>
+        </is>
+      </c>
+      <c r="G32" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H32" s="12" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I32" s="12" t="inlineStr">
+        <is>
+          <t>SKIP - redundant + new term risk</t>
+        </is>
+      </c>
+      <c r="J32" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>RealEstateAPI.com</t>
+        </is>
+      </c>
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>Listings/records/AVM/rent</t>
+        </is>
+      </c>
+      <c r="C33" s="12" t="inlineStr">
+        <is>
+          <t>Nationwide 150M+</t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>Frequent</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="inlineStr">
+        <is>
+          <t>7-day FREE TRIAL then paid (auto-convert risk)</t>
+        </is>
+      </c>
+      <c r="F33" s="12" t="inlineStr">
+        <is>
+          <t>Unverified terms. Possible RentCast alt. DO NOT sign up without owner OK.</t>
+        </is>
+      </c>
+      <c r="G33" s="12" t="inlineStr">
+        <is>
+          <t>Yes - modern API</t>
+        </is>
+      </c>
+      <c r="H33" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I33" s="12" t="inlineStr">
+        <is>
+          <t>MAYBE - report only, trial can auto-charge</t>
+        </is>
+      </c>
+      <c r="J33" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>PropMix Public Records API</t>
+        </is>
+      </c>
+      <c r="B34" s="12" t="inlineStr">
+        <is>
+          <t>Tax/deed/owner records</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="inlineStr">
+        <is>
+          <t>Nationwide 155M</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>Periodic</t>
+        </is>
+      </c>
+      <c r="E34" s="12" t="inlineStr">
+        <is>
+          <t>Paid (price not published)</t>
+        </is>
+      </c>
+      <c r="F34" s="12" t="inlineStr">
+        <is>
+          <t>Unverified terms; possible cheaper ATTOM alt.</t>
+        </is>
+      </c>
+      <c r="G34" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H34" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I34" s="12" t="inlineStr">
+        <is>
+          <t>MAYBE - report only, get quote later</t>
+        </is>
+      </c>
+      <c r="J34" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
         </is>
       </c>
     </row>
